--- a/xls/square_16_tri3_11.xlsx
+++ b/xls/square_16_tri3_11.xlsx
@@ -482,13 +482,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>1.410132312736379</v>
+        <v>1.4101329799032742</v>
       </c>
       <c r="J11">
-        <v>-1.5605968677134474</v>
+        <v>-1.560596556139253</v>
       </c>
       <c r="K11">
-        <v>-0.5989245060089432</v>
+        <v>-0.5989240757826488</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -517,13 +517,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-2.1106997387964035</v>
+        <v>-2.1106992624819916</v>
       </c>
       <c r="J12">
-        <v>-2.029941041639447</v>
+        <v>-2.0299407187965652</v>
       </c>
       <c r="K12">
-        <v>-1.3268060405258832</v>
+        <v>-1.3268058627491355</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-2.1000440553257387</v>
+        <v>-2.100045374709847</v>
       </c>
       <c r="J13">
-        <v>-2.0553876426827147</v>
+        <v>-2.0553883995736997</v>
       </c>
       <c r="K13">
-        <v>-1.3521038065646074</v>
+        <v>-1.352103683099751</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-2.0927545166740718</v>
+        <v>-2.092754961379935</v>
       </c>
       <c r="J14">
-        <v>-2.0513541471218146</v>
+        <v>-2.0513542945714636</v>
       </c>
       <c r="K14">
-        <v>-1.2954963593517765</v>
+        <v>-1.2954962929579794</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-2.0530289481436097</v>
+        <v>-2.053027804108972</v>
       </c>
       <c r="J15">
-        <v>-1.6831887559784173</v>
+        <v>-1.683188384753196</v>
       </c>
       <c r="K15">
-        <v>-0.4951117885321563</v>
+        <v>-0.4951118714711877</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-1.9101053979202185</v>
+        <v>-1.910105077634205</v>
       </c>
       <c r="J16">
-        <v>-1.5884803764070492</v>
+        <v>-1.5884803604807503</v>
       </c>
       <c r="K16">
-        <v>-0.42701973193241055</v>
+        <v>-0.4270197552825783</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-1.3660906404773734</v>
+        <v>-1.366090367435904</v>
       </c>
       <c r="J17">
-        <v>-1.0800231442735198</v>
+        <v>-1.0800230716325696</v>
       </c>
       <c r="K17">
-        <v>2.426308186037896</v>
+        <v>2.4263077389175427</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.7105515472633674</v>
+        <v>-0.7105515192345104</v>
       </c>
       <c r="J18">
-        <v>-0.5475328336765722</v>
+        <v>-0.547532823378327</v>
       </c>
       <c r="K18">
-        <v>2.9525456691082987</v>
+        <v>2.9525456784393005</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.005284038028734856</v>
+        <v>-0.005284038042524088</v>
       </c>
       <c r="J19">
-        <v>-0.005093714960493081</v>
+        <v>-0.005093714969973025</v>
       </c>
       <c r="K19">
-        <v>3.285439352941363</v>
+        <v>3.2854393532022064</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.0011114677300307805</v>
+        <v>-0.001111467729737067</v>
       </c>
       <c r="J20">
-        <v>-0.0009531391975370742</v>
+        <v>-0.0009531391973247944</v>
       </c>
       <c r="K20">
-        <v>2.898756520243293</v>
+        <v>2.898756520170516</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>8.187633844374315e-5</v>
+        <v>8.187633845974797e-5</v>
       </c>
       <c r="J21">
-        <v>3.283223969074281e-5</v>
+        <v>3.283223969768545e-5</v>
       </c>
       <c r="K21">
-        <v>2.119190534227154</v>
+        <v>2.119190534349511</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -867,13 +867,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-7.314415424512111e-5</v>
+        <v>-7.31441542462785e-5</v>
       </c>
       <c r="J22">
-        <v>-5.172388682379183e-5</v>
+        <v>-5.172388682446694e-5</v>
       </c>
       <c r="K22">
-        <v>2.161926061686787</v>
+        <v>2.1619260619437934</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -905,10 +905,10 @@
         <v>3.935642673092795e-6</v>
       </c>
       <c r="J23">
-        <v>8.480530540790651e-7</v>
+        <v>8.480530539826325e-7</v>
       </c>
       <c r="K23">
-        <v>1.673329278242583</v>
+        <v>1.6733292784801936</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -940,10 +940,10 @@
         <v>-3.9475315107329017e-7</v>
       </c>
       <c r="J24">
-        <v>-2.3381528569750277e-6</v>
+        <v>-2.3381528573607605e-6</v>
       </c>
       <c r="K24">
-        <v>1.7803024905455664</v>
+        <v>1.7803024903440108</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -972,13 +972,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>8.242485903801656e-7</v>
+        <v>8.242485902837331e-7</v>
       </c>
       <c r="J25">
-        <v>-4.899912098826879e-7</v>
+        <v>-4.899912097380387e-7</v>
       </c>
       <c r="K25">
-        <v>1.6380977750008292</v>
+        <v>1.6380977748957277</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-6.323037296334049e-7</v>
+        <v>-6.323037293441062e-7</v>
       </c>
       <c r="J26">
-        <v>-8.572865381865568e-7</v>
+        <v>-8.572865383794227e-7</v>
       </c>
       <c r="K26">
-        <v>1.5373812688369088</v>
+        <v>1.5373812688676416</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-1.2834932735712127e-7</v>
+        <v>-1.283493272124721e-7</v>
       </c>
       <c r="J27">
         <v>-2.78125759009964e-7</v>
       </c>
       <c r="K27">
-        <v>1.289729557481828</v>
+        <v>1.2897295576691084</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1080,10 +1080,10 @@
         <v>-1.505380377378867e-7</v>
       </c>
       <c r="J28">
-        <v>-1.9092014328235995e-7</v>
+        <v>-1.9092014342700914e-7</v>
       </c>
       <c r="K28">
-        <v>1.1593139705296394</v>
+        <v>1.1593139705804492</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-1.1335680983799456e-7</v>
+        <v>-1.1335680978977817e-7</v>
       </c>
       <c r="J29">
-        <v>-1.6350122215823416e-7</v>
+        <v>-1.63501222013585e-7</v>
       </c>
       <c r="K29">
-        <v>1.1408635053837017</v>
+        <v>1.140863505424698</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-5.991049564182903e-8</v>
+        <v>-5.991049549717989e-8</v>
       </c>
       <c r="J30">
-        <v>-1.612523153541703e-7</v>
+        <v>-1.612523154023867e-7</v>
       </c>
       <c r="K30">
-        <v>1.182163782525361</v>
+        <v>1.1821637825934348</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-8.600133161642929e-8</v>
+        <v>-8.600133180929481e-8</v>
       </c>
       <c r="J31">
-        <v>-1.7764035242740507e-7</v>
+        <v>-1.7764035257205424e-7</v>
       </c>
       <c r="K31">
-        <v>1.1993078361403287</v>
+        <v>1.1993078362972522</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-2.3570597791214366e-9</v>
+        <v>-2.3570596826886893e-9</v>
       </c>
       <c r="J32">
-        <v>-1.6285733116112467e-7</v>
+        <v>-1.6285733120934107e-7</v>
       </c>
       <c r="K32">
-        <v>1.2496834037629656</v>
+        <v>1.2496834035599425</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_11.xlsx
+++ b/xls/square_16_tri3_11.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>289</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>486</v>
+      </c>
+      <c r="I9">
+        <v>7.266066637554805</v>
+      </c>
+      <c r="J9">
+        <v>2.597701621904647</v>
+      </c>
+      <c r="K9">
+        <v>3.0096012695761756</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>144</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>289</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>4.674611854578255</v>
+      </c>
+      <c r="J10">
+        <v>0.822702224467956</v>
+      </c>
+      <c r="K10">
+        <v>1.6998655704593173</v>
+      </c>
+    </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>11</v>
